--- a/docs/downloads/05/tbl_latrine_alaotra_avaradrano.xlsx
+++ b/docs/downloads/05/tbl_latrine_alaotra_avaradrano.xlsx
@@ -441,12 +441,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +453,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -531,12 +519,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -548,12 +530,6 @@
         <is>
           <t>Fosse septique en individuel</t>
         </is>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>0.6</v>
       </c>
     </row>
   </sheetData>
